--- a/output/pdf_financials_xlsx/FCLI.xlsx
+++ b/output/pdf_financials_xlsx/FCLI.xlsx
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.136849</v>
+        <v>-0.136849</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.297931</v>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.136849</v>
+        <v>-0.136849</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.297931</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.136849</v>
+        <v>-0.136849</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.297931</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-3.421225</v>
+        <v>3.421225</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.136849</v>
+        <v>-0.136849</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.297931</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.136849</v>
+        <v>-0.136849</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.297931</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -2493,16 +2493,16 @@
         <v>0.071438</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.071438</v>
+        <v>0.237718</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.079934</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.938127</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.974953</v>
       </c>
     </row>
     <row r="93">
@@ -4152,7 +4152,11 @@
           <t>Reserves 15, 16</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4939,7 +4943,11 @@
           <t>Reserves 16, 17</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -5349,7 +5357,11 @@
           <t>Reserves 14, 15</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -11037,10 +11049,10 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0.136849</v>
+        <v>-0.136849</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>0.047078</v>
+        <v>-0.047078</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FCLI.xlsx
+++ b/output/pdf_financials_xlsx/FCLI.xlsx
@@ -681,13 +681,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.080904</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.021514</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001273</v>
       </c>
     </row>
     <row r="13">
@@ -1033,13 +1033,13 @@
         <v>-0.297931</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.852261</v>
+        <v>-4.933165</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.773989</v>
+        <v>-3.795503</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.033561</v>
+        <v>-3.034834</v>
       </c>
     </row>
     <row r="28">
@@ -1077,13 +1077,13 @@
         <v>-0.297931</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.790374</v>
+        <v>-4.871278</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.556095</v>
+        <v>-3.577609</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.824511</v>
+        <v>-2.825784</v>
       </c>
     </row>
     <row r="30">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-35596.54654654655</v>
+        <v>-35811.9019019019</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-406.9906440787379</v>
+        <v>-407.1740737378584</v>
       </c>
     </row>
     <row r="31">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.326993</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>2.384006</v>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.326993</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>2.384006</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">

--- a/output/pdf_financials_xlsx/FCLI.xlsx
+++ b/output/pdf_financials_xlsx/FCLI.xlsx
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.04804</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.564654</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.312606</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.248154</v>
       </c>
     </row>
     <row r="68">
@@ -3012,10 +3012,10 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.25887</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.133941</v>
       </c>
     </row>
     <row r="117">
@@ -6554,7 +6554,11 @@
           <t>Purchase of intangible assets 11</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -7366,7 +7370,11 @@
           <t>Purchase of intangible assets 12</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
